--- a/компоненты.xlsx
+++ b/компоненты.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ShiWarai\YandexDisk\Projects\small-dog\RDS-2P-blueprint\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yandex.Disk\Projects\small-dog\RDS-2P-blueprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C57DE0-E7DA-4AC9-8920-290EB34BEA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB1F93F-CBA0-4382-BE57-6E3AD2CCF541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Панда" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
   <si>
     <t>Наименование</t>
   </si>
@@ -300,6 +300,12 @@
   <si>
     <t>Опционально!</t>
   </si>
+  <si>
+    <t>Дисплей IPS 1.69''</t>
+  </si>
+  <si>
+    <t>https://ali.click/w4xao11</t>
+  </si>
 </sst>
 </file>
 
@@ -308,7 +314,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0[$₽-419];\-#,##0.0[$₽-419]"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1164,18 +1170,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" customWidth="1"/>
-    <col min="4" max="4" width="55.81640625" customWidth="1"/>
-    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="55.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="16.5" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A2" s="23" t="s">
         <v>33</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>16755</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A3" s="24" t="s">
         <v>34</v>
       </c>
@@ -1233,7 +1239,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="44.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="46.5" thickTop="1" thickBot="1">
       <c r="A4" s="25" t="s">
         <v>35</v>
       </c>
@@ -1247,14 +1253,14 @@
         <v>36</v>
       </c>
       <c r="E4" s="36">
-        <v>7579</v>
+        <v>6000</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" si="0"/>
-        <v>90948</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A5" s="26" t="s">
         <v>43</v>
       </c>
@@ -1273,7 +1279,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A6" s="27" t="s">
         <v>5</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A7" s="26" t="s">
         <v>38</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A9" s="25" t="s">
         <v>42</v>
       </c>
@@ -1351,7 +1357,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A10" s="25" t="s">
         <v>14</v>
       </c>
@@ -1370,7 +1376,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A11" s="24" t="s">
         <v>8</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A12" s="24" t="s">
         <v>45</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
@@ -1427,7 +1433,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A14" s="32" t="s">
         <v>18</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A15" s="32" t="s">
         <v>19</v>
       </c>
@@ -1465,7 +1471,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A16" s="32" t="s">
         <v>20</v>
       </c>
@@ -1484,7 +1490,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A17" s="32" t="s">
         <v>21</v>
       </c>
@@ -1506,7 +1512,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A18" s="32" t="s">
         <v>22</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A19" s="34" t="s">
         <v>25</v>
       </c>
@@ -1547,7 +1553,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A20" s="34" t="s">
         <v>26</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A21" s="32" t="s">
         <v>23</v>
       </c>
@@ -1585,7 +1591,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A22" s="44" t="s">
         <v>47</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A23" s="34" t="s">
         <v>50</v>
       </c>
@@ -1623,7 +1629,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="29.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" ht="30.75" thickTop="1" thickBot="1">
       <c r="A24" s="34" t="s">
         <v>52</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="29.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="45" thickTop="1" thickBot="1">
       <c r="A25" s="34" t="s">
         <v>53</v>
       </c>
@@ -1663,7 +1669,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A26" s="34" t="s">
         <v>57</v>
       </c>
@@ -1682,7 +1688,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A27" s="34" t="s">
         <v>58</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A28" s="34" t="s">
         <v>59</v>
       </c>
@@ -1722,7 +1728,7 @@
         <v>3698</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A29" s="34" t="s">
         <v>60</v>
       </c>
@@ -1743,7 +1749,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" ht="31.5" thickTop="1" thickBot="1">
       <c r="A30" s="34" t="s">
         <v>67</v>
       </c>
@@ -1762,7 +1768,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A31" s="34" t="s">
         <v>69</v>
       </c>
@@ -1780,7 +1786,7 @@
       </c>
       <c r="F31" s="35"/>
     </row>
-    <row r="32" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A32" s="34" t="s">
         <v>70</v>
       </c>
@@ -1794,7 +1800,7 @@
       </c>
       <c r="F32" s="35"/>
     </row>
-    <row r="33" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A33" s="34" t="s">
         <v>74</v>
       </c>
@@ -1810,7 +1816,7 @@
       </c>
       <c r="F33" s="35"/>
     </row>
-    <row r="34" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
       <c r="A34" s="34" t="s">
         <v>71</v>
       </c>
@@ -1824,35 +1830,50 @@
       </c>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="33" t="s">
+    <row r="35" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
+      <c r="A35" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="13">
-        <v>1</v>
-      </c>
-      <c r="C35" s="52"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="51"/>
       <c r="D35" s="31" t="s">
         <v>73</v>
       </c>
       <c r="E35" s="49">
         <v>251</v>
       </c>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.5" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="E36" t="s">
+      <c r="F35" s="35"/>
+    </row>
+    <row r="36" spans="1:6" ht="17.25" thickTop="1" thickBot="1">
+      <c r="A36" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="13">
+        <v>1</v>
+      </c>
+      <c r="C36" s="52"/>
+      <c r="D36" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="49">
+        <f>269+89</f>
+        <v>358</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickTop="1">
+      <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="42">
-        <f>SUM(F2:F35)</f>
-        <v>132799</v>
+      <c r="F37" s="42">
+        <f>SUM(F2:F36)</f>
+        <v>113851</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C31:C36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{E8E6A088-3663-4BBA-96B2-C577F265BF6E}"/>
